--- a/input.xlsx
+++ b/input.xlsx
@@ -1,19 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="raukos"/>
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="0" windowHeight="0" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:revision xmlns:pm="smNativeData" day="1792945505" val="1234" rev="124" rev64="64" revOS="3" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1792945505" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1792945505" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1792945505"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>nrosobowy</t>
   </si>
@@ -31,18 +41,6 @@
   </si>
   <si>
     <t>nr_domu</t>
-  </si>
-  <si>
-    <t>Johm Deere</t>
-  </si>
-  <si>
-    <t>38-120</t>
-  </si>
-  <si>
-    <t>Czudec</t>
-  </si>
-  <si>
-    <t>Kolejowa</t>
   </si>
   <si>
     <t>Kimirse</t>
@@ -61,127 +59,249 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;zł&quot;;\-#,##0\ &quot;zł&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;zł&quot;;[Red]\-#,##0\ &quot;zł&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;zł&quot;;\-#,##0.00\ &quot;zł&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;zł&quot;;[Red]\-#,##0.00\ &quot;zł&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;zł&quot;_-;\-* #,##0\ &quot;zł&quot;_-;_-* &quot;-&quot;\ &quot;zł&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _z_ł_-;\-* #,##0\ _z_ł_-;_-* &quot;-&quot;\ _z_ł_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _z_ł_-;\-* #,##0.00\ _z_ł_-;_-* &quot;-&quot;??\ _z_ł_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1792945505" ulstyle="none" kern="1">
+            <pm:latin face="Calibri" sz="220" lang="default"/>
+            <pm:cs face="Basic Roman" sz="220" lang="default"/>
+            <pm:ea face="Basic Roman" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
+      <name val="Basic Sans"/>
+      <family val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1792945505" ulstyle="none" kern="1">
+            <pm:latin face="Basic Sans" sz="200" lang="default"/>
+            <pm:cs face="Basic Roman" sz="200" lang="default"/>
+            <pm:ea face="Basic Roman" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor indexed="64"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1792945505" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1792945505"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1792945505"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0"/>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:charStyles xmlns:pm="smNativeData" id="1792945505" count="1">
+        <pm:charStyle name="Normalny" fontId="0" Id="1"/>
+      </pm:charStyles>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Craft">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Craft">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="EEECE1"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="1F497D"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Craft">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:ea typeface="Basic Roman"/>
+        <a:cs typeface="Basic Roman"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Craft">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -190,39 +310,136 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr>
+        <a:prstTxWarp prst="textNoShape">
+          <a:avLst/>
+        </a:prstTxWarp>
+        <a:noAutofit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr>
+          <a:defRPr/>
+        </a:defPPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15.40"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -242,9 +459,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2">
-        <v>1002</v>
+    <row r="2" spans="1:6">
+      <c r="A2" t="n">
+        <v>2829</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -258,32 +475,35 @@
       <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2829</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3">
+      <c r="F2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup orientation="portrait"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1792945505" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1792945505" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1792945505" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1792945505" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>